--- a/artfynd/A 61178-2025 artfynd.xlsx
+++ b/artfynd/A 61178-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103382212</v>
+        <v>114012160</v>
       </c>
       <c r="B2" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768840.9911639878</v>
+        <v>768821</v>
       </c>
       <c r="R2" t="n">
-        <v>7525867.181800777</v>
+        <v>7525122</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103382210</v>
+        <v>114012155</v>
       </c>
       <c r="B3" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768820.8801959448</v>
+        <v>768940</v>
       </c>
       <c r="R3" t="n">
-        <v>7525884.206223659</v>
+        <v>7525631</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -910,16 +880,11 @@
         <v>103382256</v>
       </c>
       <c r="B4" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768874.9459626281</v>
+        <v>768875</v>
       </c>
       <c r="R4" t="n">
-        <v>7525189.868561864</v>
+        <v>7525190</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103382257</v>
+        <v>103382212</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768902.8025517624</v>
+        <v>768841</v>
       </c>
       <c r="R5" t="n">
-        <v>7525179.369813014</v>
+        <v>7525867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103382258</v>
+        <v>103382257</v>
       </c>
       <c r="B6" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768898.9673494073</v>
+        <v>768903</v>
       </c>
       <c r="R6" t="n">
-        <v>7525183.177135632</v>
+        <v>7525179</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114012158</v>
+        <v>103382258</v>
       </c>
       <c r="B7" t="n">
-        <v>96616</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768917</v>
+        <v>768899</v>
       </c>
       <c r="R7" t="n">
-        <v>7525226</v>
+        <v>7525183</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1361,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114012159</v>
+        <v>103382210</v>
       </c>
       <c r="B8" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768823</v>
+        <v>768821</v>
       </c>
       <c r="R8" t="n">
-        <v>7525117</v>
+        <v>7525884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1470,12 +1385,7 @@
         <v>114012154</v>
       </c>
       <c r="B9" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114012160</v>
+        <v>114012159</v>
       </c>
       <c r="B10" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768821</v>
+        <v>768823</v>
       </c>
       <c r="R10" t="n">
-        <v>7525122</v>
+        <v>7525117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114012155</v>
+        <v>114012158</v>
       </c>
       <c r="B11" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1719,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768940</v>
+        <v>768917</v>
       </c>
       <c r="R11" t="n">
-        <v>7525631</v>
+        <v>7525226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 61178-2025 artfynd.xlsx
+++ b/artfynd/A 61178-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114012160</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114012155</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103382256</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103382212</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103382257</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103382258</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103382210</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114012154</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114012159</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,8 +1732,25 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114012158</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>